--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -323,9 +323,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -395,7 +394,7 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -757,7 +756,7 @@
         <v>192.1</v>
       </c>
       <c r="E5" s="6">
-        <v>1.231</v>
+        <v>1.23</v>
       </c>
       <c r="F5" s="4">
         <v>17</v>
@@ -777,7 +776,7 @@
         <v>257.2</v>
       </c>
       <c r="E6" s="6">
-        <v>1.114</v>
+        <v>1.11</v>
       </c>
       <c r="F6" s="4">
         <v>11</v>
@@ -797,7 +796,7 @@
         <v>94.3</v>
       </c>
       <c r="E7" s="6">
-        <v>1.247</v>
+        <v>1.25</v>
       </c>
       <c r="F7" s="4">
         <v>9</v>
@@ -817,7 +816,7 @@
         <v>110.8</v>
       </c>
       <c r="E8" s="6">
-        <v>1.158</v>
+        <v>1.16</v>
       </c>
       <c r="F8" s="4">
         <v>7</v>
@@ -837,7 +836,7 @@
         <v>51.3</v>
       </c>
       <c r="E9" s="6">
-        <v>1.312</v>
+        <v>1.31</v>
       </c>
       <c r="F9" s="4">
         <v>6</v>
@@ -857,7 +856,7 @@
         <v>115.3</v>
       </c>
       <c r="E10" s="6">
-        <v>1.092</v>
+        <v>1.09</v>
       </c>
       <c r="F10" s="4">
         <v>4</v>
@@ -877,7 +876,7 @@
         <v>59.5</v>
       </c>
       <c r="E11" s="6">
-        <v>1.122</v>
+        <v>1.12</v>
       </c>
       <c r="F11" s="4">
         <v>3</v>
@@ -897,7 +896,7 @@
         <v>37.9</v>
       </c>
       <c r="E12" s="6">
-        <v>1.161</v>
+        <v>1.16</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -917,7 +916,7 @@
         <v>169.8</v>
       </c>
       <c r="E13" s="6">
-        <v>1.034</v>
+        <v>1.03</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -937,7 +936,7 @@
         <v>111</v>
       </c>
       <c r="E14" s="6">
-        <v>1.048</v>
+        <v>1.05</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
@@ -957,7 +956,7 @@
         <v>61</v>
       </c>
       <c r="E15" s="6">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -977,7 +976,7 @@
         <v>50.7</v>
       </c>
       <c r="E16" s="6">
-        <v>1.044</v>
+        <v>1.04</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -94,16 +94,16 @@
     <t>Marrowfield Surgical Services</t>
   </si>
   <si>
+    <t>41210</t>
+  </si>
+  <si>
+    <t>Alderbrook General Medicine</t>
+  </si>
+  <si>
     <t>41510</t>
   </si>
   <si>
     <t>Carrowdean General Medicine</t>
-  </si>
-  <si>
-    <t>41210</t>
-  </si>
-  <si>
-    <t>Alderbrook General Medicine</t>
   </si>
   <si>
     <t>41320</t>
@@ -750,16 +750,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2305</v>
+        <v>2352</v>
       </c>
       <c r="D5" s="5">
-        <v>192.1</v>
+        <v>203.1</v>
       </c>
       <c r="E5" s="6">
         <v>1.23</v>
       </c>
       <c r="F5" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,16 +770,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3367</v>
+        <v>3597</v>
       </c>
       <c r="D6" s="5">
-        <v>257.2</v>
+        <v>278.9</v>
       </c>
       <c r="E6" s="6">
         <v>1.11</v>
       </c>
       <c r="F6" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -793,13 +793,13 @@
         <v>1162</v>
       </c>
       <c r="D7" s="5">
-        <v>94.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="F7" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,16 +810,16 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="D8" s="5">
-        <v>110.8</v>
+        <v>109.2</v>
       </c>
       <c r="E8" s="6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="F8" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -830,13 +830,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D9" s="5">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="E9" s="6">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="F9" s="4">
         <v>6</v>
@@ -853,10 +853,10 @@
         <v>1257</v>
       </c>
       <c r="D10" s="5">
-        <v>115.3</v>
+        <v>118.1</v>
       </c>
       <c r="E10" s="6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="F10" s="4">
         <v>4</v>
@@ -870,16 +870,16 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D11" s="5">
-        <v>59.5</v>
+        <v>58.9</v>
       </c>
       <c r="E11" s="6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="F11" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,13 +890,13 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>466</v>
+        <v>2079</v>
       </c>
       <c r="D12" s="5">
-        <v>37.9</v>
+        <v>169.8</v>
       </c>
       <c r="E12" s="6">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -910,13 +910,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>2077</v>
+        <v>466</v>
       </c>
       <c r="D13" s="5">
-        <v>169.8</v>
+        <v>38.5</v>
       </c>
       <c r="E13" s="6">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -930,16 +930,16 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D14" s="5">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E14" s="6">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="F14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -950,16 +950,16 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D15" s="5">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="E15" s="6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="F15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>652</v>
       </c>
       <c r="D16" s="5">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
       <c r="E16" s="6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1011,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1067,13 +1067,13 @@
         <v>44</v>
       </c>
       <c r="B5" s="4">
-        <v>36993</v>
+        <v>38247</v>
       </c>
       <c r="C5" s="4">
-        <v>4069</v>
+        <v>4016</v>
       </c>
       <c r="D5" s="5">
-        <v>113.4</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,13 +1081,13 @@
         <v>45</v>
       </c>
       <c r="B6" s="4">
-        <v>21621</v>
+        <v>23182</v>
       </c>
       <c r="C6" s="4">
-        <v>2432</v>
+        <v>2526</v>
       </c>
       <c r="D6" s="5">
-        <v>115.8</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1095,13 +1095,13 @@
         <v>46</v>
       </c>
       <c r="B7" s="4">
-        <v>15037</v>
+        <v>19733</v>
       </c>
       <c r="C7" s="4">
-        <v>1598</v>
+        <v>2015</v>
       </c>
       <c r="D7" s="5">
-        <v>112.8</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,13 +1109,13 @@
         <v>47</v>
       </c>
       <c r="B8" s="4">
-        <v>2304</v>
+        <v>2340</v>
       </c>
       <c r="C8" s="4">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D8" s="5">
-        <v>112.4</v>
+        <v>111.5</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +1162,7 @@
         <v>901</v>
       </c>
       <c r="C5" s="4">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1173,7 +1173,7 @@
         <v>793</v>
       </c>
       <c r="C6" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
         <v>832</v>
       </c>
       <c r="C7" s="4">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1195,7 +1195,7 @@
         <v>918</v>
       </c>
       <c r="C8" s="4">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1206,7 +1206,7 @@
         <v>908</v>
       </c>
       <c r="C9" s="4">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1217,7 +1217,7 @@
         <v>808</v>
       </c>
       <c r="C10" s="4">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1228,7 +1228,7 @@
         <v>819</v>
       </c>
       <c r="C11" s="4">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1239,7 +1239,7 @@
         <v>900</v>
       </c>
       <c r="C12" s="4">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1250,7 +1250,7 @@
         <v>917</v>
       </c>
       <c r="C13" s="4">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
         <v>809</v>
       </c>
       <c r="C14" s="4">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>1922</v>
+        <v>2078</v>
       </c>
       <c r="D5" s="4">
-        <v>969</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1304</v>
+        <v>1404</v>
       </c>
       <c r="D6" s="4">
-        <v>652</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1122</v>
+        <v>1257</v>
       </c>
       <c r="D7" s="4">
-        <v>582</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>76</v>
       </c>
       <c r="C8" s="4">
-        <v>1252</v>
+        <v>1456</v>
       </c>
       <c r="D8" s="4">
-        <v>643</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>1489</v>
+        <v>1621</v>
       </c>
       <c r="D9" s="4">
-        <v>728</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>1456</v>
+        <v>1695</v>
       </c>
       <c r="D10" s="4">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="D11" s="4">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>955</v>
+        <v>1068</v>
       </c>
       <c r="D12" s="4">
-        <v>465</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -750,10 +750,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2352</v>
+        <v>2360</v>
       </c>
       <c r="D5" s="5">
-        <v>203.1</v>
+        <v>203.8</v>
       </c>
       <c r="E5" s="6">
         <v>1.23</v>
@@ -770,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3597</v>
+        <v>3609</v>
       </c>
       <c r="D6" s="5">
-        <v>278.9</v>
+        <v>279.9</v>
       </c>
       <c r="E6" s="6">
         <v>1.11</v>
@@ -810,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D8" s="5">
-        <v>109.2</v>
+        <v>109.1</v>
       </c>
       <c r="E8" s="6">
         <v>1.15</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D11" s="5">
         <v>58.9</v>
@@ -1073,7 +1073,7 @@
         <v>4016</v>
       </c>
       <c r="D5" s="5">
-        <v>108.9</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1087,7 +1087,7 @@
         <v>2526</v>
       </c>
       <c r="D6" s="5">
-        <v>112.1</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1101,7 +1101,7 @@
         <v>2015</v>
       </c>
       <c r="D7" s="5">
-        <v>110.2</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1115,7 +1115,7 @@
         <v>234</v>
       </c>
       <c r="D8" s="5">
-        <v>111.5</v>
+        <v>111.6</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -106,16 +106,16 @@
     <t>Carrowdean General Medicine</t>
   </si>
   <si>
+    <t>41410</t>
+  </si>
+  <si>
+    <t>Marrowfield Orthopaedics</t>
+  </si>
+  <si>
     <t>41320</t>
   </si>
   <si>
     <t>Stonecreek General Surgery</t>
-  </si>
-  <si>
-    <t>41410</t>
-  </si>
-  <si>
-    <t>Marrowfield Orthopaedics</t>
   </si>
   <si>
     <t>41430</t>
@@ -750,10 +750,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="D5" s="5">
-        <v>203.8</v>
+        <v>203.6</v>
       </c>
       <c r="E5" s="6">
         <v>1.23</v>
@@ -770,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3609</v>
+        <v>3602</v>
       </c>
       <c r="D6" s="5">
-        <v>279.9</v>
+        <v>279.3</v>
       </c>
       <c r="E6" s="6">
         <v>1.11</v>
@@ -810,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D8" s="5">
-        <v>109.1</v>
+        <v>109</v>
       </c>
       <c r="E8" s="6">
         <v>1.15</v>
@@ -850,10 +850,10 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>1257</v>
+        <v>1305</v>
       </c>
       <c r="D10" s="5">
-        <v>118.1</v>
+        <v>122.6</v>
       </c>
       <c r="E10" s="6">
         <v>1.08</v>
@@ -870,16 +870,16 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>776</v>
+        <v>825</v>
       </c>
       <c r="D11" s="5">
-        <v>58.9</v>
+        <v>62.6</v>
       </c>
       <c r="E11" s="6">
         <v>1.11</v>
       </c>
       <c r="F11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,10 +890,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="D12" s="5">
-        <v>169.8</v>
+        <v>169.7</v>
       </c>
       <c r="E12" s="6">
         <v>1.03</v>
@@ -930,13 +930,13 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>1471</v>
+        <v>703</v>
       </c>
       <c r="D14" s="5">
-        <v>114</v>
+        <v>58.9</v>
       </c>
       <c r="E14" s="6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -950,13 +950,13 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>734</v>
+        <v>1357</v>
       </c>
       <c r="D15" s="5">
-        <v>61.5</v>
+        <v>105.2</v>
       </c>
       <c r="E15" s="6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="F15" s="4">
         <v>1</v>
@@ -970,10 +970,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="D16" s="5">
-        <v>51.2</v>
+        <v>52.4</v>
       </c>
       <c r="E16" s="6">
         <v>1.03</v>
@@ -1098,7 +1098,7 @@
         <v>19733</v>
       </c>
       <c r="C7" s="4">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D7" s="5">
         <v>110.3</v>
@@ -1340,7 +1340,7 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D7" s="4">
         <v>653</v>
@@ -1368,7 +1368,7 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="D9" s="4">
         <v>833</v>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -750,10 +750,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="D5" s="5">
-        <v>203.6</v>
+        <v>203.9</v>
       </c>
       <c r="E5" s="6">
         <v>1.23</v>
@@ -870,10 +870,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D11" s="5">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="E11" s="6">
         <v>1.11</v>
@@ -1067,10 +1067,10 @@
         <v>44</v>
       </c>
       <c r="B5" s="4">
-        <v>38247</v>
+        <v>38249</v>
       </c>
       <c r="C5" s="4">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="D5" s="5">
         <v>109</v>
@@ -1081,10 +1081,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="4">
-        <v>23182</v>
+        <v>23179</v>
       </c>
       <c r="C6" s="4">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="D6" s="5">
         <v>112.2</v>
@@ -1184,7 +1184,7 @@
         <v>832</v>
       </c>
       <c r="C7" s="4">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>2078</v>
+        <v>2070</v>
       </c>
       <c r="D5" s="4">
-        <v>1001</v>
+        <v>997</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="D6" s="4">
-        <v>695</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="D7" s="4">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>76</v>
       </c>
       <c r="C8" s="4">
-        <v>1456</v>
+        <v>1447</v>
       </c>
       <c r="D8" s="4">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="D9" s="4">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>1695</v>
+        <v>1683</v>
       </c>
       <c r="D10" s="4">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D11" s="4">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>1068</v>
+        <v>1058</v>
       </c>
       <c r="D12" s="4">
-        <v>490</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -52,16 +52,22 @@
     <t>Complications avoided</t>
   </si>
   <si>
+    <t>41220</t>
+  </si>
+  <si>
+    <t>Alderbrook General Surgery</t>
+  </si>
+  <si>
     <t>41230</t>
   </si>
   <si>
     <t>Alderbrook Orthopaedics</t>
   </si>
   <si>
-    <t>41220</t>
-  </si>
-  <si>
-    <t>Alderbrook General Surgery</t>
+    <t>41210</t>
+  </si>
+  <si>
+    <t>Alderbrook General Medicine</t>
   </si>
   <si>
     <t>41420</t>
@@ -82,6 +88,12 @@
     <t>Stonecreek Vascular Surgery</t>
   </si>
   <si>
+    <t>41510</t>
+  </si>
+  <si>
+    <t>Carrowdean General Medicine</t>
+  </si>
+  <si>
     <t>41240</t>
   </si>
   <si>
@@ -94,46 +106,34 @@
     <t>Marrowfield Surgical Services</t>
   </si>
   <si>
-    <t>41210</t>
-  </si>
-  <si>
-    <t>Alderbrook General Medicine</t>
-  </si>
-  <si>
-    <t>41510</t>
-  </si>
-  <si>
-    <t>Carrowdean General Medicine</t>
-  </si>
-  <si>
     <t>41410</t>
   </si>
   <si>
     <t>Marrowfield Orthopaedics</t>
   </si>
   <si>
+    <t>41430</t>
+  </si>
+  <si>
+    <t>Stonecreek Renal Medicine</t>
+  </si>
+  <si>
     <t>41320</t>
   </si>
   <si>
     <t>Stonecreek General Surgery</t>
   </si>
   <si>
-    <t>41430</t>
-  </si>
-  <si>
-    <t>Stonecreek Renal Medicine</t>
-  </si>
-  <si>
     <t>Recommendation</t>
   </si>
   <si>
+    <t>Alderbrook General Surgery (41220)</t>
+  </si>
+  <si>
+    <t>Closest unit</t>
+  </si>
+  <si>
     <t>Alderbrook Orthopaedics (41230)</t>
-  </si>
-  <si>
-    <t>Closest unit</t>
-  </si>
-  <si>
-    <t>Alderbrook General Surgery (41220)</t>
   </si>
   <si>
     <t>Complications avoided there</t>
@@ -750,16 +750,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2359</v>
+        <v>3560</v>
       </c>
       <c r="D5" s="5">
-        <v>203.9</v>
+        <v>276.1</v>
       </c>
       <c r="E5" s="6">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="F5" s="4">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,16 +770,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3602</v>
+        <v>2305</v>
       </c>
       <c r="D6" s="5">
-        <v>279.3</v>
+        <v>199.2</v>
       </c>
       <c r="E6" s="6">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="F6" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -790,13 +790,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>1162</v>
+        <v>2077</v>
       </c>
       <c r="D7" s="5">
-        <v>92.09999999999999</v>
+        <v>169.7</v>
       </c>
       <c r="E7" s="6">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="F7" s="4">
         <v>8</v>
@@ -810,16 +810,16 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1364</v>
+        <v>1162</v>
       </c>
       <c r="D8" s="5">
-        <v>109</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E8" s="6">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="F8" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -830,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>508</v>
+        <v>1364</v>
       </c>
       <c r="D9" s="5">
-        <v>50.7</v>
+        <v>109</v>
       </c>
       <c r="E9" s="6">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="F9" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,16 +850,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>1305</v>
+        <v>506</v>
       </c>
       <c r="D10" s="5">
-        <v>122.6</v>
+        <v>50.5</v>
       </c>
       <c r="E10" s="6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="F10" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,16 +870,16 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>823</v>
+        <v>466</v>
       </c>
       <c r="D11" s="5">
-        <v>62.4</v>
+        <v>38.5</v>
       </c>
       <c r="E11" s="6">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="F11" s="4">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,16 +890,16 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>2077</v>
+        <v>1257</v>
       </c>
       <c r="D12" s="5">
-        <v>169.7</v>
+        <v>118.1</v>
       </c>
       <c r="E12" s="6">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="F12" s="4">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -910,16 +910,16 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>466</v>
+        <v>779</v>
       </c>
       <c r="D13" s="5">
-        <v>38.5</v>
+        <v>59.1</v>
       </c>
       <c r="E13" s="6">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F13" s="4">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -930,16 +930,16 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>703</v>
+        <v>734</v>
       </c>
       <c r="D14" s="5">
-        <v>58.9</v>
+        <v>61.5</v>
       </c>
       <c r="E14" s="6">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="F14" s="4">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -950,16 +950,16 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>1357</v>
+        <v>652</v>
       </c>
       <c r="D15" s="5">
-        <v>105.2</v>
+        <v>51.2</v>
       </c>
       <c r="E15" s="6">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="F15" s="4">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,16 +970,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>667</v>
+        <v>1469</v>
       </c>
       <c r="D16" s="5">
-        <v>52.4</v>
+        <v>113.9</v>
       </c>
       <c r="E16" s="6">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="F16" s="4">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1011,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1067,13 +1067,13 @@
         <v>44</v>
       </c>
       <c r="B5" s="4">
-        <v>38249</v>
+        <v>46925</v>
       </c>
       <c r="C5" s="4">
-        <v>4017</v>
+        <v>4841</v>
       </c>
       <c r="D5" s="5">
-        <v>109</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,13 +1081,13 @@
         <v>45</v>
       </c>
       <c r="B6" s="4">
-        <v>23179</v>
+        <v>29194</v>
       </c>
       <c r="C6" s="4">
-        <v>2525</v>
+        <v>3626</v>
       </c>
       <c r="D6" s="5">
-        <v>112.2</v>
+        <v>126.8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1095,13 +1095,13 @@
         <v>46</v>
       </c>
       <c r="B7" s="4">
-        <v>19733</v>
+        <v>23903</v>
       </c>
       <c r="C7" s="4">
-        <v>2016</v>
+        <v>2522</v>
       </c>
       <c r="D7" s="5">
-        <v>110.3</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1112,10 +1112,10 @@
         <v>2340</v>
       </c>
       <c r="C8" s="4">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D8" s="5">
-        <v>111.6</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>2070</v>
+        <v>2742</v>
       </c>
       <c r="D5" s="4">
-        <v>997</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1410</v>
+        <v>1839</v>
       </c>
       <c r="D6" s="4">
-        <v>686</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1263</v>
+        <v>1618</v>
       </c>
       <c r="D7" s="4">
-        <v>658</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>76</v>
       </c>
       <c r="C8" s="4">
-        <v>1447</v>
+        <v>1854</v>
       </c>
       <c r="D8" s="4">
-        <v>725</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>1633</v>
+        <v>2192</v>
       </c>
       <c r="D9" s="4">
-        <v>825</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>1683</v>
+        <v>2178</v>
       </c>
       <c r="D10" s="4">
-        <v>808</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>866</v>
+        <v>1093</v>
       </c>
       <c r="D11" s="4">
-        <v>430</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>1058</v>
+        <v>1225</v>
       </c>
       <c r="D12" s="4">
-        <v>478</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -52,16 +52,52 @@
     <t>Complications avoided</t>
   </si>
   <si>
+    <t>41230</t>
+  </si>
+  <si>
+    <t>Alderbrook Orthopaedics</t>
+  </si>
+  <si>
     <t>41220</t>
   </si>
   <si>
     <t>Alderbrook General Surgery</t>
   </si>
   <si>
-    <t>41230</t>
-  </si>
-  <si>
-    <t>Alderbrook Orthopaedics</t>
+    <t>41420</t>
+  </si>
+  <si>
+    <t>Marrowfield General Medicine</t>
+  </si>
+  <si>
+    <t>41310</t>
+  </si>
+  <si>
+    <t>Stonecreek General Medicine</t>
+  </si>
+  <si>
+    <t>41330</t>
+  </si>
+  <si>
+    <t>Stonecreek Vascular Surgery</t>
+  </si>
+  <si>
+    <t>41240</t>
+  </si>
+  <si>
+    <t>Alderbrook Respiratory Medicine</t>
+  </si>
+  <si>
+    <t>41520</t>
+  </si>
+  <si>
+    <t>Marrowfield Surgical Services</t>
+  </si>
+  <si>
+    <t>41510</t>
+  </si>
+  <si>
+    <t>Carrowdean General Medicine</t>
   </si>
   <si>
     <t>41210</t>
@@ -70,40 +106,10 @@
     <t>Alderbrook General Medicine</t>
   </si>
   <si>
-    <t>41420</t>
-  </si>
-  <si>
-    <t>Marrowfield General Medicine</t>
-  </si>
-  <si>
-    <t>41310</t>
-  </si>
-  <si>
-    <t>Stonecreek General Medicine</t>
-  </si>
-  <si>
-    <t>41330</t>
-  </si>
-  <si>
-    <t>Stonecreek Vascular Surgery</t>
-  </si>
-  <si>
-    <t>41510</t>
-  </si>
-  <si>
-    <t>Carrowdean General Medicine</t>
-  </si>
-  <si>
-    <t>41240</t>
-  </si>
-  <si>
-    <t>Alderbrook Respiratory Medicine</t>
-  </si>
-  <si>
-    <t>41520</t>
-  </si>
-  <si>
-    <t>Marrowfield Surgical Services</t>
+    <t>41320</t>
+  </si>
+  <si>
+    <t>Stonecreek General Surgery</t>
   </si>
   <si>
     <t>41410</t>
@@ -118,22 +124,16 @@
     <t>Stonecreek Renal Medicine</t>
   </si>
   <si>
-    <t>41320</t>
-  </si>
-  <si>
-    <t>Stonecreek General Surgery</t>
-  </si>
-  <si>
     <t>Recommendation</t>
   </si>
   <si>
+    <t>Alderbrook Orthopaedics (41230)</t>
+  </si>
+  <si>
+    <t>Closest unit</t>
+  </si>
+  <si>
     <t>Alderbrook General Surgery (41220)</t>
-  </si>
-  <si>
-    <t>Closest unit</t>
-  </si>
-  <si>
-    <t>Alderbrook Orthopaedics (41230)</t>
   </si>
   <si>
     <t>Complications avoided there</t>
@@ -750,16 +750,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>3560</v>
+        <v>2305</v>
       </c>
       <c r="D5" s="5">
-        <v>276.1</v>
+        <v>199.2</v>
       </c>
       <c r="E5" s="6">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="F5" s="4">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,16 +770,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>2305</v>
+        <v>3560</v>
       </c>
       <c r="D6" s="5">
-        <v>199.2</v>
+        <v>276.1</v>
       </c>
       <c r="E6" s="6">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="F6" s="4">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -790,16 +790,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>2077</v>
+        <v>1162</v>
       </c>
       <c r="D7" s="5">
-        <v>169.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="F7" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,16 +810,16 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1162</v>
+        <v>1362</v>
       </c>
       <c r="D8" s="5">
-        <v>92.09999999999999</v>
+        <v>108.8</v>
       </c>
       <c r="E8" s="6">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="F8" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -830,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>1364</v>
+        <v>506</v>
       </c>
       <c r="D9" s="5">
-        <v>109</v>
+        <v>50.5</v>
       </c>
       <c r="E9" s="6">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="F9" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,16 +850,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>506</v>
+        <v>1257</v>
       </c>
       <c r="D10" s="5">
-        <v>50.5</v>
+        <v>118.1</v>
       </c>
       <c r="E10" s="6">
         <v>1.1</v>
       </c>
       <c r="F10" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,16 +870,16 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>466</v>
+        <v>779</v>
       </c>
       <c r="D11" s="5">
-        <v>38.5</v>
+        <v>59.1</v>
       </c>
       <c r="E11" s="6">
-        <v>0.95</v>
+        <v>1.13</v>
       </c>
       <c r="F11" s="4">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,16 +890,16 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>1257</v>
+        <v>466</v>
       </c>
       <c r="D12" s="5">
-        <v>118.1</v>
+        <v>38.5</v>
       </c>
       <c r="E12" s="6">
-        <v>0.98</v>
+        <v>1.19</v>
       </c>
       <c r="F12" s="4">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -910,16 +910,16 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>779</v>
+        <v>1979</v>
       </c>
       <c r="D13" s="5">
-        <v>59.1</v>
+        <v>161.7</v>
       </c>
       <c r="E13" s="6">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="F13" s="4">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -930,16 +930,16 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>734</v>
+        <v>1469</v>
       </c>
       <c r="D14" s="5">
-        <v>61.5</v>
+        <v>113.9</v>
       </c>
       <c r="E14" s="6">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="F14" s="4">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -950,16 +950,16 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>652</v>
+        <v>734</v>
       </c>
       <c r="D15" s="5">
-        <v>51.2</v>
+        <v>61.5</v>
       </c>
       <c r="E15" s="6">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="F15" s="4">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,16 +970,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>1469</v>
+        <v>717</v>
       </c>
       <c r="D16" s="5">
-        <v>113.9</v>
+        <v>56.3</v>
       </c>
       <c r="E16" s="6">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="F16" s="4">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1011,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1070,10 +1070,10 @@
         <v>46925</v>
       </c>
       <c r="C5" s="4">
-        <v>4841</v>
+        <v>4893</v>
       </c>
       <c r="D5" s="5">
-        <v>105.2</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1084,10 +1084,10 @@
         <v>29194</v>
       </c>
       <c r="C6" s="4">
-        <v>3626</v>
+        <v>3856</v>
       </c>
       <c r="D6" s="5">
-        <v>126.8</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1098,10 +1098,10 @@
         <v>23903</v>
       </c>
       <c r="C7" s="4">
-        <v>2522</v>
+        <v>2650</v>
       </c>
       <c r="D7" s="5">
-        <v>113.1</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1112,10 +1112,10 @@
         <v>2340</v>
       </c>
       <c r="C8" s="4">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="D8" s="5">
-        <v>91.09999999999999</v>
+        <v>114.5</v>
       </c>
     </row>
   </sheetData>
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>2742</v>
+        <v>2843</v>
       </c>
       <c r="D5" s="4">
-        <v>1299</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1839</v>
+        <v>1906</v>
       </c>
       <c r="D6" s="4">
-        <v>859</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1618</v>
+        <v>1681</v>
       </c>
       <c r="D7" s="4">
-        <v>775</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>76</v>
       </c>
       <c r="C8" s="4">
-        <v>1854</v>
+        <v>1908</v>
       </c>
       <c r="D8" s="4">
-        <v>930</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>2192</v>
+        <v>2269</v>
       </c>
       <c r="D9" s="4">
-        <v>1022</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>2178</v>
+        <v>2241</v>
       </c>
       <c r="D10" s="4">
-        <v>1062</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="D11" s="4">
-        <v>553</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="D12" s="4">
-        <v>585</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -770,16 +770,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3560</v>
+        <v>3529</v>
       </c>
       <c r="D6" s="5">
-        <v>276.1</v>
+        <v>273.7</v>
       </c>
       <c r="E6" s="6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="F6" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1362</v>
+        <v>1340</v>
       </c>
       <c r="D8" s="5">
-        <v>108.8</v>
+        <v>107.1</v>
       </c>
       <c r="E8" s="6">
         <v>1.16</v>
@@ -830,10 +830,10 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D9" s="5">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="E9" s="6">
         <v>1.31</v>
@@ -910,16 +910,16 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>1979</v>
+        <v>2162</v>
       </c>
       <c r="D13" s="5">
-        <v>161.7</v>
+        <v>176.6</v>
       </c>
       <c r="E13" s="6">
         <v>1.04</v>
       </c>
       <c r="F13" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,10 +970,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="D16" s="5">
-        <v>56.3</v>
+        <v>55.5</v>
       </c>
       <c r="E16" s="6">
         <v>1.06</v>
@@ -1011,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1067,13 +1067,13 @@
         <v>44</v>
       </c>
       <c r="B5" s="4">
-        <v>46925</v>
+        <v>48656</v>
       </c>
       <c r="C5" s="4">
-        <v>4893</v>
+        <v>5555</v>
       </c>
       <c r="D5" s="5">
-        <v>106.3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,13 +1081,13 @@
         <v>45</v>
       </c>
       <c r="B6" s="4">
-        <v>29194</v>
+        <v>26850</v>
       </c>
       <c r="C6" s="4">
-        <v>3856</v>
+        <v>3159</v>
       </c>
       <c r="D6" s="5">
-        <v>134.8</v>
+        <v>119.3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1095,13 +1095,13 @@
         <v>46</v>
       </c>
       <c r="B7" s="4">
-        <v>23903</v>
+        <v>24519</v>
       </c>
       <c r="C7" s="4">
-        <v>2650</v>
+        <v>2669</v>
       </c>
       <c r="D7" s="5">
-        <v>118.8</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>2843</v>
+        <v>2829</v>
       </c>
       <c r="D5" s="4">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="D6" s="4">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1681</v>
+        <v>1675</v>
       </c>
       <c r="D7" s="4">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1357,7 +1357,7 @@
         <v>1908</v>
       </c>
       <c r="D8" s="4">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>2269</v>
+        <v>2274</v>
       </c>
       <c r="D9" s="4">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="D10" s="4">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="D11" s="4">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,7 +1410,7 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="4">
         <v>605</v>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -750,16 +750,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2305</v>
+        <v>2103</v>
       </c>
       <c r="D5" s="5">
-        <v>199.2</v>
+        <v>181.7</v>
       </c>
       <c r="E5" s="6">
         <v>1.24</v>
       </c>
       <c r="F5" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3529</v>
+        <v>3462</v>
       </c>
       <c r="D6" s="5">
-        <v>273.7</v>
+        <v>268.5</v>
       </c>
       <c r="E6" s="6">
         <v>1.11</v>
@@ -790,16 +790,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>1162</v>
+        <v>1229</v>
       </c>
       <c r="D7" s="5">
-        <v>92.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E7" s="6">
         <v>1.25</v>
       </c>
       <c r="F7" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1340</v>
+        <v>1297</v>
       </c>
       <c r="D8" s="5">
-        <v>107.1</v>
+        <v>103.6</v>
       </c>
       <c r="E8" s="6">
         <v>1.16</v>
@@ -830,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>502</v>
+        <v>544</v>
       </c>
       <c r="D9" s="5">
-        <v>50.1</v>
+        <v>54.3</v>
       </c>
       <c r="E9" s="6">
         <v>1.31</v>
       </c>
       <c r="F9" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>1257</v>
+        <v>1227</v>
       </c>
       <c r="D10" s="5">
-        <v>118.1</v>
+        <v>115.3</v>
       </c>
       <c r="E10" s="6">
         <v>1.1</v>
@@ -870,10 +870,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="D11" s="5">
-        <v>59.1</v>
+        <v>58.5</v>
       </c>
       <c r="E11" s="6">
         <v>1.13</v>
@@ -890,10 +890,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="D12" s="5">
-        <v>38.5</v>
+        <v>40.4</v>
       </c>
       <c r="E12" s="6">
         <v>1.19</v>
@@ -910,10 +910,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>2162</v>
+        <v>2279</v>
       </c>
       <c r="D13" s="5">
-        <v>176.6</v>
+        <v>186.2</v>
       </c>
       <c r="E13" s="6">
         <v>1.04</v>
@@ -930,10 +930,10 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>1469</v>
+        <v>1402</v>
       </c>
       <c r="D14" s="5">
-        <v>113.9</v>
+        <v>108.7</v>
       </c>
       <c r="E14" s="6">
         <v>1.05</v>
@@ -950,10 +950,10 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>734</v>
+        <v>786</v>
       </c>
       <c r="D15" s="5">
-        <v>61.5</v>
+        <v>65.8</v>
       </c>
       <c r="E15" s="6">
         <v>1.09</v>
@@ -970,10 +970,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="D16" s="5">
-        <v>55.5</v>
+        <v>56.3</v>
       </c>
       <c r="E16" s="6">
         <v>1.06</v>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -750,16 +750,16 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2103</v>
+        <v>2196</v>
       </c>
       <c r="D5" s="5">
-        <v>181.7</v>
+        <v>189.8</v>
       </c>
       <c r="E5" s="6">
         <v>1.24</v>
       </c>
       <c r="F5" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3462</v>
+        <v>3506</v>
       </c>
       <c r="D6" s="5">
-        <v>268.5</v>
+        <v>271.9</v>
       </c>
       <c r="E6" s="6">
         <v>1.11</v>
@@ -790,16 +790,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>1229</v>
+        <v>1157</v>
       </c>
       <c r="D7" s="5">
-        <v>97.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="E7" s="6">
         <v>1.25</v>
       </c>
       <c r="F7" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1297</v>
+        <v>1342</v>
       </c>
       <c r="D8" s="5">
-        <v>103.6</v>
+        <v>107.2</v>
       </c>
       <c r="E8" s="6">
         <v>1.16</v>
@@ -830,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>544</v>
+        <v>503</v>
       </c>
       <c r="D9" s="5">
-        <v>54.3</v>
+        <v>50.2</v>
       </c>
       <c r="E9" s="6">
         <v>1.31</v>
       </c>
       <c r="F9" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>1227</v>
+        <v>1257</v>
       </c>
       <c r="D10" s="5">
-        <v>115.3</v>
+        <v>118.1</v>
       </c>
       <c r="E10" s="6">
         <v>1.1</v>
@@ -870,10 +870,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D11" s="5">
-        <v>58.5</v>
+        <v>59</v>
       </c>
       <c r="E11" s="6">
         <v>1.13</v>
@@ -890,10 +890,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="D12" s="5">
-        <v>40.4</v>
+        <v>38.5</v>
       </c>
       <c r="E12" s="6">
         <v>1.19</v>
@@ -910,10 +910,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>2279</v>
+        <v>2142</v>
       </c>
       <c r="D13" s="5">
-        <v>186.2</v>
+        <v>175</v>
       </c>
       <c r="E13" s="6">
         <v>1.04</v>
@@ -930,10 +930,10 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>1402</v>
+        <v>1468</v>
       </c>
       <c r="D14" s="5">
-        <v>108.7</v>
+        <v>113.8</v>
       </c>
       <c r="E14" s="6">
         <v>1.05</v>
@@ -950,10 +950,10 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>786</v>
+        <v>734</v>
       </c>
       <c r="D15" s="5">
-        <v>65.8</v>
+        <v>61.5</v>
       </c>
       <c r="E15" s="6">
         <v>1.09</v>
@@ -970,10 +970,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>717</v>
+        <v>691</v>
       </c>
       <c r="D16" s="5">
-        <v>56.3</v>
+        <v>54.3</v>
       </c>
       <c r="E16" s="6">
         <v>1.06</v>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -94,16 +94,16 @@
     <t>Marrowfield Surgical Services</t>
   </si>
   <si>
+    <t>41210</t>
+  </si>
+  <si>
+    <t>Alderbrook General Medicine</t>
+  </si>
+  <si>
     <t>41510</t>
   </si>
   <si>
     <t>Carrowdean General Medicine</t>
-  </si>
-  <si>
-    <t>41210</t>
-  </si>
-  <si>
-    <t>Alderbrook General Medicine</t>
   </si>
   <si>
     <t>41320</t>
@@ -750,10 +750,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="D5" s="5">
-        <v>189.8</v>
+        <v>189.4</v>
       </c>
       <c r="E5" s="6">
         <v>1.24</v>
@@ -770,13 +770,13 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3506</v>
+        <v>3579</v>
       </c>
       <c r="D6" s="5">
-        <v>271.9</v>
+        <v>275.6</v>
       </c>
       <c r="E6" s="6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="F6" s="4">
         <v>15</v>
@@ -790,10 +790,10 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D7" s="5">
-        <v>91.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E7" s="6">
         <v>1.25</v>
@@ -810,10 +810,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="D8" s="5">
-        <v>107.2</v>
+        <v>108.2</v>
       </c>
       <c r="E8" s="6">
         <v>1.16</v>
@@ -830,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="D9" s="5">
-        <v>50.2</v>
+        <v>51.8</v>
       </c>
       <c r="E9" s="6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="F9" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -853,7 +853,7 @@
         <v>1257</v>
       </c>
       <c r="D10" s="5">
-        <v>118.1</v>
+        <v>116.8</v>
       </c>
       <c r="E10" s="6">
         <v>1.1</v>
@@ -870,10 +870,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D11" s="5">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="E11" s="6">
         <v>1.13</v>
@@ -890,13 +890,13 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>466</v>
+        <v>2077</v>
       </c>
       <c r="D12" s="5">
-        <v>38.5</v>
+        <v>171.4</v>
       </c>
       <c r="E12" s="6">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="F12" s="4">
         <v>4</v>
@@ -910,13 +910,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>2142</v>
+        <v>466</v>
       </c>
       <c r="D13" s="5">
-        <v>175</v>
+        <v>38.8</v>
       </c>
       <c r="E13" s="6">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="F13" s="4">
         <v>4</v>
@@ -930,13 +930,13 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>1468</v>
+        <v>1451</v>
       </c>
       <c r="D14" s="5">
-        <v>113.8</v>
+        <v>113.3</v>
       </c>
       <c r="E14" s="6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="F14" s="4">
         <v>3</v>
@@ -950,10 +950,10 @@
         <v>29</v>
       </c>
       <c r="C15" s="4">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D15" s="5">
-        <v>61.5</v>
+        <v>61.1</v>
       </c>
       <c r="E15" s="6">
         <v>1.09</v>
@@ -970,10 +970,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="D16" s="5">
-        <v>54.3</v>
+        <v>53.8</v>
       </c>
       <c r="E16" s="6">
         <v>1.06</v>
@@ -1067,13 +1067,13 @@
         <v>44</v>
       </c>
       <c r="B5" s="4">
-        <v>48656</v>
+        <v>48617</v>
       </c>
       <c r="C5" s="4">
-        <v>5555</v>
+        <v>5553</v>
       </c>
       <c r="D5" s="5">
-        <v>116</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,13 +1081,13 @@
         <v>45</v>
       </c>
       <c r="B6" s="4">
-        <v>26850</v>
+        <v>26869</v>
       </c>
       <c r="C6" s="4">
         <v>3159</v>
       </c>
       <c r="D6" s="5">
-        <v>119.3</v>
+        <v>119.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1095,13 +1095,13 @@
         <v>46</v>
       </c>
       <c r="B7" s="4">
-        <v>24519</v>
+        <v>24533</v>
       </c>
       <c r="C7" s="4">
-        <v>2669</v>
+        <v>2637</v>
       </c>
       <c r="D7" s="5">
-        <v>118.4</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,13 +1109,13 @@
         <v>47</v>
       </c>
       <c r="B8" s="4">
-        <v>2340</v>
+        <v>2323</v>
       </c>
       <c r="C8" s="4">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D8" s="5">
-        <v>114.5</v>
+        <v>113.7</v>
       </c>
     </row>
   </sheetData>
@@ -1159,10 +1159,10 @@
         <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="C5" s="4">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1170,10 +1170,10 @@
         <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="C6" s="4">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1181,10 +1181,10 @@
         <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="C7" s="4">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1192,10 +1192,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="C8" s="4">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1203,10 +1203,10 @@
         <v>57</v>
       </c>
       <c r="B9" s="4">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="C9" s="4">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1214,10 +1214,10 @@
         <v>58</v>
       </c>
       <c r="B10" s="4">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="C10" s="4">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1225,10 +1225,10 @@
         <v>59</v>
       </c>
       <c r="B11" s="4">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="C11" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1236,10 +1236,10 @@
         <v>60</v>
       </c>
       <c r="B12" s="4">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="C12" s="4">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1247,10 +1247,10 @@
         <v>61</v>
       </c>
       <c r="B13" s="4">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="C13" s="4">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1258,10 +1258,10 @@
         <v>62</v>
       </c>
       <c r="B14" s="4">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="C14" s="4">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>2829</v>
+        <v>2837</v>
       </c>
       <c r="D5" s="4">
-        <v>1348</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1901</v>
+        <v>1945</v>
       </c>
       <c r="D6" s="4">
-        <v>932</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1675</v>
+        <v>1710</v>
       </c>
       <c r="D7" s="4">
-        <v>846</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>76</v>
       </c>
       <c r="C8" s="4">
-        <v>1908</v>
+        <v>1824</v>
       </c>
       <c r="D8" s="4">
-        <v>975</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>2274</v>
+        <v>2074</v>
       </c>
       <c r="D9" s="4">
-        <v>1058</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>2236</v>
+        <v>2277</v>
       </c>
       <c r="D10" s="4">
-        <v>1110</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>1088</v>
+        <v>1172</v>
       </c>
       <c r="D11" s="4">
-        <v>563</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>1248</v>
+        <v>1259</v>
       </c>
       <c r="D12" s="4">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -70,16 +70,16 @@
     <t>Marrowfield General Medicine</t>
   </si>
   <si>
+    <t>41330</t>
+  </si>
+  <si>
+    <t>Stonecreek Vascular Surgery</t>
+  </si>
+  <si>
     <t>41310</t>
   </si>
   <si>
     <t>Stonecreek General Medicine</t>
-  </si>
-  <si>
-    <t>41330</t>
-  </si>
-  <si>
-    <t>Stonecreek Vascular Surgery</t>
   </si>
   <si>
     <t>41240</t>
@@ -756,10 +756,10 @@
         <v>189.4</v>
       </c>
       <c r="E5" s="6">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="F5" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,16 +770,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>3579</v>
+        <v>3516</v>
       </c>
       <c r="D6" s="5">
-        <v>275.6</v>
+        <v>270.7</v>
       </c>
       <c r="E6" s="6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="F6" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -790,16 +790,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>1158</v>
+        <v>1179</v>
       </c>
       <c r="D7" s="5">
-        <v>91.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="F7" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -810,16 +810,16 @@
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1347</v>
+        <v>506</v>
       </c>
       <c r="D8" s="5">
-        <v>108.2</v>
+        <v>51.1</v>
       </c>
       <c r="E8" s="6">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="F8" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -830,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
-        <v>513</v>
+        <v>1365</v>
       </c>
       <c r="D9" s="5">
-        <v>51.8</v>
+        <v>109.6</v>
       </c>
       <c r="E9" s="6">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="F9" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,16 +850,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D10" s="5">
-        <v>116.8</v>
+        <v>116.6</v>
       </c>
       <c r="E10" s="6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="F10" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,13 +870,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="D11" s="5">
-        <v>58.1</v>
+        <v>58.8</v>
       </c>
       <c r="E11" s="6">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="F11" s="4">
         <v>4</v>
@@ -890,16 +890,16 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>2077</v>
+        <v>2060</v>
       </c>
       <c r="D12" s="5">
-        <v>171.4</v>
+        <v>170</v>
       </c>
       <c r="E12" s="6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="F12" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -910,16 +910,16 @@
         <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D13" s="5">
-        <v>38.8</v>
+        <v>38.4</v>
       </c>
       <c r="E13" s="6">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="F13" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -930,13 +930,13 @@
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>1451</v>
+        <v>1470</v>
       </c>
       <c r="D14" s="5">
-        <v>113.3</v>
+        <v>114.8</v>
       </c>
       <c r="E14" s="6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="F14" s="4">
         <v>3</v>
@@ -956,10 +956,10 @@
         <v>61.1</v>
       </c>
       <c r="E15" s="6">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="F15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,16 +970,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>678</v>
+        <v>639</v>
       </c>
       <c r="D16" s="5">
-        <v>53.8</v>
+        <v>50.7</v>
       </c>
       <c r="E16" s="6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="F16" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1011,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1070,10 +1070,10 @@
         <v>48617</v>
       </c>
       <c r="C5" s="4">
-        <v>5553</v>
+        <v>5488</v>
       </c>
       <c r="D5" s="5">
-        <v>116.1</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1084,10 +1084,10 @@
         <v>26869</v>
       </c>
       <c r="C6" s="4">
-        <v>3159</v>
+        <v>3138</v>
       </c>
       <c r="D6" s="5">
-        <v>119.5</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1098,10 +1098,10 @@
         <v>24533</v>
       </c>
       <c r="C7" s="4">
-        <v>2637</v>
+        <v>2676</v>
       </c>
       <c r="D7" s="5">
-        <v>118.2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1112,10 +1112,10 @@
         <v>2323</v>
       </c>
       <c r="C8" s="4">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D8" s="5">
-        <v>113.7</v>
+        <v>109.4</v>
       </c>
     </row>
   </sheetData>
@@ -1312,10 +1312,10 @@
         <v>70</v>
       </c>
       <c r="C5" s="4">
-        <v>2837</v>
+        <v>2826</v>
       </c>
       <c r="D5" s="4">
-        <v>1380</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>72</v>
       </c>
       <c r="C6" s="4">
-        <v>1945</v>
+        <v>1926</v>
       </c>
       <c r="D6" s="4">
-        <v>899</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>74</v>
       </c>
       <c r="C7" s="4">
-        <v>1710</v>
+        <v>1684</v>
       </c>
       <c r="D7" s="4">
-        <v>861</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>76</v>
       </c>
       <c r="C8" s="4">
-        <v>1824</v>
+        <v>1791</v>
       </c>
       <c r="D8" s="4">
-        <v>952</v>
+        <v>966</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>78</v>
       </c>
       <c r="C9" s="4">
-        <v>2074</v>
+        <v>2064</v>
       </c>
       <c r="D9" s="4">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>2277</v>
+        <v>2272</v>
       </c>
       <c r="D10" s="4">
-        <v>1166</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="4">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D11" s="4">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>84</v>
       </c>
       <c r="C12" s="4">
-        <v>1259</v>
+        <v>1270</v>
       </c>
       <c r="D12" s="4">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Notes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Placement'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Placement'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,9 +26,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
-  <si>
-    <t>Cycle IP-10 placement: complications a placement would avoid, by unit</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+  <si>
+    <t>Cycle IP-10 placement: avoidable complications by unit</t>
   </si>
   <si>
     <t>Quarter from 1 April 2027. Eligible units under charter clause 4.2. Prepared by Clinical Improvement, 18 March 2027.</t>
@@ -46,10 +46,13 @@
     <t>Expected complications</t>
   </si>
   <si>
-    <t>Standardised ratio, specification period</t>
-  </si>
-  <si>
-    <t>Complications avoided</t>
+    <t>Standardised ratio, published rates</t>
+  </si>
+  <si>
+    <t>Standardised ratio, the network's own rates</t>
+  </si>
+  <si>
+    <t>Avoidable complications</t>
   </si>
   <si>
     <t>41230</t>
@@ -58,72 +61,72 @@
     <t>Alderbrook Orthopaedics</t>
   </si>
   <si>
+    <t>41420</t>
+  </si>
+  <si>
+    <t>Marrowfield General Medicine</t>
+  </si>
+  <si>
+    <t>41410</t>
+  </si>
+  <si>
+    <t>Marrowfield Orthopaedics</t>
+  </si>
+  <si>
+    <t>41330</t>
+  </si>
+  <si>
+    <t>Stonecreek Vascular Surgery</t>
+  </si>
+  <si>
+    <t>41310</t>
+  </si>
+  <si>
+    <t>Stonecreek General Medicine</t>
+  </si>
+  <si>
+    <t>41320</t>
+  </si>
+  <si>
+    <t>Stonecreek General Surgery</t>
+  </si>
+  <si>
+    <t>41510</t>
+  </si>
+  <si>
+    <t>Carrowdean General Medicine</t>
+  </si>
+  <si>
+    <t>41520</t>
+  </si>
+  <si>
+    <t>Marrowfield Surgical Services</t>
+  </si>
+  <si>
+    <t>41430</t>
+  </si>
+  <si>
+    <t>Stonecreek Renal Medicine</t>
+  </si>
+  <si>
+    <t>41240</t>
+  </si>
+  <si>
+    <t>Alderbrook Respiratory Medicine</t>
+  </si>
+  <si>
     <t>41220</t>
   </si>
   <si>
     <t>Alderbrook General Surgery</t>
   </si>
   <si>
-    <t>41420</t>
-  </si>
-  <si>
-    <t>Marrowfield General Medicine</t>
-  </si>
-  <si>
-    <t>41330</t>
-  </si>
-  <si>
-    <t>Stonecreek Vascular Surgery</t>
-  </si>
-  <si>
-    <t>41310</t>
-  </si>
-  <si>
-    <t>Stonecreek General Medicine</t>
-  </si>
-  <si>
-    <t>41240</t>
-  </si>
-  <si>
-    <t>Alderbrook Respiratory Medicine</t>
-  </si>
-  <si>
-    <t>41520</t>
-  </si>
-  <si>
-    <t>Marrowfield Surgical Services</t>
-  </si>
-  <si>
     <t>41210</t>
   </si>
   <si>
     <t>Alderbrook General Medicine</t>
   </si>
   <si>
-    <t>41510</t>
-  </si>
-  <si>
-    <t>Carrowdean General Medicine</t>
-  </si>
-  <si>
-    <t>41320</t>
-  </si>
-  <si>
-    <t>Stonecreek General Surgery</t>
-  </si>
-  <si>
-    <t>41410</t>
-  </si>
-  <si>
-    <t>Marrowfield Orthopaedics</t>
-  </si>
-  <si>
-    <t>41430</t>
-  </si>
-  <si>
-    <t>Stonecreek Renal Medicine</t>
-  </si>
-  <si>
     <t>Recommendation</t>
   </si>
   <si>
@@ -133,10 +136,10 @@
     <t>Closest unit</t>
   </si>
   <si>
-    <t>Alderbrook General Surgery (41220)</t>
-  </si>
-  <si>
-    <t>Complications avoided there</t>
+    <t>Marrowfield General Medicine (41420)</t>
+  </si>
+  <si>
+    <t>Avoidable complications there</t>
   </si>
   <si>
     <t>Gap</t>
@@ -304,7 +307,13 @@
     <t>Specification 3.2 and 3.3, over every closed quarter from 1 July 2024.</t>
   </si>
   <si>
-    <t>Charter clause 4.3, over the assessment quarter.</t>
+    <t>Charter clause 4.3: the complications the unit's own patients had, less the complications that patients of the same risk band and age band ordinarily have, counted patient by patient and summed, then carried onto the separations planned for the assessment quarter.</t>
+  </si>
+  <si>
+    <t>The network's own rates</t>
+  </si>
+  <si>
+    <t>Complications per in-scope episode by risk band and age band, from the episode extract over the ten closed quarters of specification 4.0. The rates published with the specification were derived from activity in the year ended 30 June 2024 and clause 3.1 does not re-estimate them; the network's own rates now run from 0.89 to 1.32 of them, band by band.</t>
   </si>
   <si>
     <t>Cost centre 41510</t>
@@ -701,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C83909B-F06D-5D55-A847-62EED7ED39D9}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -709,20 +718,21 @@
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -741,285 +751,324 @@
       <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2305</v>
+      </c>
+      <c r="D5" s="5">
+        <v>198.4</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1.1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="G5" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1089</v>
+      </c>
+      <c r="D6" s="5">
+        <v>86</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="G6" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4">
+        <v>734</v>
+      </c>
+      <c r="D7" s="5">
+        <v>57</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1.15</v>
+      </c>
+      <c r="G7" s="4">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2200</v>
-      </c>
-      <c r="D5" s="5">
-        <v>189.4</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="F5" s="4">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3516</v>
-      </c>
-      <c r="D6" s="5">
-        <v>270.7</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1.07</v>
-      </c>
-      <c r="F6" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1179</v>
-      </c>
-      <c r="D7" s="5">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F7" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="D8" s="5">
-        <v>51.1</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="F8" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.23</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1.04</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4">
         <v>1365</v>
       </c>
       <c r="D9" s="5">
-        <v>109.6</v>
+        <v>109.7</v>
       </c>
       <c r="E9" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="F9" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.03</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1.02</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
-        <v>1255</v>
+        <v>1470</v>
       </c>
       <c r="D10" s="5">
-        <v>116.6</v>
+        <v>114.8</v>
       </c>
       <c r="E10" s="6">
-        <v>1.07</v>
-      </c>
-      <c r="F10" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.24</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1.01</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4">
-        <v>788</v>
+        <v>465</v>
       </c>
       <c r="D11" s="5">
-        <v>58.8</v>
+        <v>29.6</v>
       </c>
       <c r="E11" s="6">
-        <v>1.09</v>
-      </c>
-      <c r="F11" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.05</v>
+      </c>
+      <c r="F11" s="6">
+        <v>1.01</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" s="4">
-        <v>2060</v>
+        <v>779</v>
       </c>
       <c r="D12" s="5">
-        <v>170</v>
+        <v>58.1</v>
       </c>
       <c r="E12" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.23</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="4">
-        <v>462</v>
+        <v>652</v>
       </c>
       <c r="D13" s="5">
-        <v>38.4</v>
+        <v>49.9</v>
       </c>
       <c r="E13" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.98</v>
+      </c>
+      <c r="G13" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="4">
-        <v>1470</v>
+        <v>1275</v>
       </c>
       <c r="D14" s="5">
-        <v>114.8</v>
+        <v>118.5</v>
       </c>
       <c r="E14" s="6">
-        <v>1.04</v>
-      </c>
-      <c r="F14" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.98</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="G14" s="4">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4">
-        <v>735</v>
+        <v>3560</v>
       </c>
       <c r="D15" s="5">
-        <v>61.1</v>
+        <v>274.1</v>
       </c>
       <c r="E15" s="6">
-        <v>1.06</v>
-      </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.22</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="G15" s="4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="4">
-        <v>639</v>
+        <v>2077</v>
       </c>
       <c r="D16" s="5">
-        <v>50.7</v>
+        <v>171.4</v>
       </c>
       <c r="E16" s="6">
-        <v>1.04</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="G16" s="4">
+        <v>-5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1040,82 +1089,82 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>48617</v>
       </c>
       <c r="C5" s="4">
-        <v>5488</v>
+        <v>4909</v>
       </c>
       <c r="D5" s="5">
-        <v>114.7</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
-        <v>26869</v>
+        <v>26848</v>
       </c>
       <c r="C6" s="4">
-        <v>3138</v>
+        <v>2738</v>
       </c>
       <c r="D6" s="5">
-        <v>118.7</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
-        <v>24533</v>
+        <v>24522</v>
       </c>
       <c r="C7" s="4">
-        <v>2676</v>
+        <v>2294</v>
       </c>
       <c r="D7" s="5">
-        <v>120</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
-        <v>2323</v>
+        <v>2306</v>
       </c>
       <c r="C8" s="4">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="D8" s="5">
-        <v>109.4</v>
+        <v>111.7</v>
       </c>
     </row>
   </sheetData>
@@ -1135,31 +1184,31 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="C5" s="4">
         <v>45</v>
@@ -1167,10 +1216,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C6" s="4">
         <v>45</v>
@@ -1178,32 +1227,32 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="C7" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="C8" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>930</v>
+        <v>908</v>
       </c>
       <c r="C9" s="4">
         <v>41</v>
@@ -1211,43 +1260,43 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="4">
-        <v>825</v>
+        <v>808</v>
       </c>
       <c r="C10" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="4">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="C11" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="C12" s="4">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="4">
-        <v>931</v>
+        <v>917</v>
       </c>
       <c r="C13" s="4">
         <v>37</v>
@@ -1255,13 +1304,13 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="4">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="C14" s="4">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1282,138 +1331,138 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4">
-        <v>2826</v>
+        <v>2500</v>
       </c>
       <c r="D5" s="4">
-        <v>1368</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4">
-        <v>1926</v>
+        <v>1594</v>
       </c>
       <c r="D6" s="4">
-        <v>884</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4">
-        <v>1684</v>
+        <v>1336</v>
       </c>
       <c r="D7" s="4">
-        <v>849</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4">
-        <v>1791</v>
+        <v>1688</v>
       </c>
       <c r="D8" s="4">
-        <v>966</v>
+        <v>775</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4">
-        <v>2064</v>
+        <v>1797</v>
       </c>
       <c r="D9" s="4">
-        <v>1102</v>
+        <v>907</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="4">
-        <v>2272</v>
+        <v>1927</v>
       </c>
       <c r="D10" s="4">
-        <v>1159</v>
+        <v>962</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="4">
-        <v>1175</v>
+        <v>1082</v>
       </c>
       <c r="D11" s="4">
-        <v>536</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="4">
-        <v>1270</v>
+        <v>1250</v>
       </c>
       <c r="D12" s="4">
-        <v>616</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DAD7A38-DFBD-538A-8480-FFFCF534114D}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -1432,18 +1481,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1451,39 +1500,47 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
   <si>
-    <t>Cycle IP-10 placement: avoidable complications by unit</t>
+    <t>Cycle IP-11 placement: avoidable complications by unit</t>
   </si>
   <si>
     <t>Quarter from 1 April 2027. Eligible units under charter clause 4.2. Prepared by Clinical Improvement, 18 March 2027.</t>
@@ -295,7 +295,7 @@
     <t>Eligible units</t>
   </si>
   <si>
-    <t>Charter clause 4.2: acute inpatient units with four or more closed quarters on specification 4.0 and no placement in the previous twelve closed quarters. Twelve units qualify for cycle IP-10.</t>
+    <t>Charter clause 4.2: acute inpatient units with four or more closed quarters on specification 4.0 and no placement in the previous twelve closed quarters. Twelve units qualify for cycle IP-11.</t>
   </si>
   <si>
     <t>Specification 3.4: planned separations times the unit's expected complications per separation over the specification period to date.</t>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Cycle IP-11 placement: avoidable complications by unit</t>
   </si>
@@ -145,22 +145,25 @@
     <t>Gap</t>
   </si>
   <si>
-    <t>Adjusted complication rate by hospital, year ended 31 December 2026</t>
-  </si>
-  <si>
-    <t>In-scope episodes under specification 4.0, counted at the site each unit reported under in the month of separation.</t>
+    <t>What the complication indicator excludes, by hospital, year ended 31 December 2026</t>
+  </si>
+  <si>
+    <t>Separations as the activity summary reports them, all care types, counted at the site each unit reported under in the month. Excluded separations are those the summary reports less the episodes the indicator measured under specification 4.0 clauses 2.1 to 2.3.</t>
   </si>
   <si>
     <t>Hospital</t>
   </si>
   <si>
-    <t>In-scope episodes</t>
-  </si>
-  <si>
-    <t>Complications</t>
-  </si>
-  <si>
-    <t>Adjusted rate per 1,000 episodes</t>
+    <t>Separations reported</t>
+  </si>
+  <si>
+    <t>Episodes the indicator measured</t>
+  </si>
+  <si>
+    <t>Separations excluded</t>
+  </si>
+  <si>
+    <t>Excluded with a complication</t>
   </si>
   <si>
     <t>Alderbrook Hospital</t>
@@ -1078,26 +1081,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD3E515-5036-5D01-9BB2-0785FB2DA474}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1110,61 +1114,76 @@
       <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4">
+        <v>53192</v>
+      </c>
+      <c r="C5" s="4">
         <v>48617</v>
       </c>
-      <c r="C5" s="4">
-        <v>4909</v>
-      </c>
-      <c r="D5" s="5">
-        <v>102.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <v>4575</v>
+      </c>
+      <c r="E5" s="4">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4">
+        <v>29383</v>
+      </c>
+      <c r="C6" s="4">
         <v>26848</v>
       </c>
-      <c r="C6" s="4">
-        <v>2738</v>
-      </c>
-      <c r="D6" s="5">
-        <v>103.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="4">
+        <v>2535</v>
+      </c>
+      <c r="E6" s="4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4">
+        <v>27562</v>
+      </c>
+      <c r="C7" s="4">
         <v>24522</v>
       </c>
-      <c r="C7" s="4">
-        <v>2294</v>
-      </c>
-      <c r="D7" s="5">
-        <v>103.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="4">
+        <v>3040</v>
+      </c>
+      <c r="E7" s="4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="4">
+        <v>2533</v>
+      </c>
+      <c r="C8" s="4">
         <v>2306</v>
       </c>
-      <c r="C8" s="4">
-        <v>199</v>
-      </c>
-      <c r="D8" s="5">
-        <v>111.7</v>
+      <c r="D8" s="4">
+        <v>227</v>
+      </c>
+      <c r="E8" s="4">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1184,28 +1203,28 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>901</v>
@@ -1216,7 +1235,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>793</v>
@@ -1227,7 +1246,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>832</v>
@@ -1238,7 +1257,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>918</v>
@@ -1249,7 +1268,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>908</v>
@@ -1260,7 +1279,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4">
         <v>808</v>
@@ -1271,7 +1290,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
         <v>819</v>
@@ -1282,7 +1301,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4">
         <v>900</v>
@@ -1293,7 +1312,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="4">
         <v>917</v>
@@ -1304,7 +1323,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>809</v>
@@ -1331,34 +1350,34 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4">
         <v>2500</v>
@@ -1369,10 +1388,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4">
         <v>1594</v>
@@ -1383,10 +1402,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4">
         <v>1336</v>
@@ -1397,10 +1416,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4">
         <v>1688</v>
@@ -1411,10 +1430,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="4">
         <v>1797</v>
@@ -1425,10 +1444,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="4">
         <v>1927</v>
@@ -1439,10 +1458,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" s="4">
         <v>1082</v>
@@ -1453,10 +1472,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" s="4">
         <v>1250</v>
@@ -1481,18 +1500,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1500,15 +1519,15 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1516,31 +1535,31 @@
         <v>8</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="99">
   <si>
     <t>Cycle IP-11 placement: avoidable complications by unit</t>
   </si>
@@ -148,16 +148,10 @@
     <t>What the complication indicator excludes, by hospital, year ended 31 December 2026</t>
   </si>
   <si>
-    <t>Separations as the activity summary reports them, all care types, counted at the site each unit reported under in the month. Excluded separations are those the summary reports less the episodes the indicator measured under specification 4.0 clauses 2.1 to 2.3.</t>
+    <t>The separations the activity summary reports, all care types, less the episodes the indicator measured under specification 4.0 clauses 2.1 to 2.3, counted at the site each unit reported under in the month. The episode extract is one row per record the warehouse received and is not the authority on separations.</t>
   </si>
   <si>
     <t>Hospital</t>
-  </si>
-  <si>
-    <t>Separations reported</t>
-  </si>
-  <si>
-    <t>Episodes the indicator measured</t>
   </si>
   <si>
     <t>Separations excluded</t>
@@ -1081,27 +1075,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD3E515-5036-5D01-9BB2-0785FB2DA474}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1111,78 +1103,48 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B5" s="4">
+        <v>4575</v>
+      </c>
+      <c r="C5" s="4">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B6" s="4">
+        <v>2535</v>
+      </c>
+      <c r="C6" s="4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="4">
-        <v>53192</v>
-      </c>
-      <c r="C5" s="4">
-        <v>48617</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4575</v>
-      </c>
-      <c r="E5" s="4">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B7" s="4">
+        <v>3040</v>
+      </c>
+      <c r="C7" s="4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="4">
-        <v>29383</v>
-      </c>
-      <c r="C6" s="4">
-        <v>26848</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2535</v>
-      </c>
-      <c r="E6" s="4">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="4">
-        <v>27562</v>
-      </c>
-      <c r="C7" s="4">
-        <v>24522</v>
-      </c>
-      <c r="D7" s="4">
-        <v>3040</v>
-      </c>
-      <c r="E7" s="4">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
       <c r="B8" s="4">
-        <v>2533</v>
+        <v>227</v>
       </c>
       <c r="C8" s="4">
-        <v>2306</v>
-      </c>
-      <c r="D8" s="4">
-        <v>227</v>
-      </c>
-      <c r="E8" s="4">
         <v>13</v>
       </c>
     </row>
@@ -1203,28 +1165,28 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>901</v>
@@ -1235,7 +1197,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>793</v>
@@ -1246,7 +1208,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>832</v>
@@ -1257,7 +1219,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>918</v>
@@ -1268,7 +1230,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="4">
         <v>908</v>
@@ -1279,7 +1241,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="4">
         <v>808</v>
@@ -1290,7 +1252,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B11" s="4">
         <v>819</v>
@@ -1301,7 +1263,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B12" s="4">
         <v>900</v>
@@ -1312,7 +1274,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B13" s="4">
         <v>917</v>
@@ -1323,7 +1285,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" s="4">
         <v>809</v>
@@ -1350,34 +1312,34 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4">
         <v>2500</v>
@@ -1388,10 +1350,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4">
         <v>1594</v>
@@ -1402,10 +1364,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4">
         <v>1336</v>
@@ -1416,10 +1378,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4">
         <v>1688</v>
@@ -1430,10 +1392,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" s="4">
         <v>1797</v>
@@ -1444,10 +1406,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C10" s="4">
         <v>1927</v>
@@ -1458,10 +1420,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4">
         <v>1082</v>
@@ -1472,10 +1434,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4">
         <v>1250</v>
@@ -1500,18 +1462,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1519,15 +1481,15 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1535,31 +1497,31 @@
         <v>8</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/task194/golden/embed_placement_2027q4.xlsx
+++ b/task194/golden/embed_placement_2027q4.xlsx
@@ -319,7 +319,7 @@
     <t>Developing the record</t>
   </si>
   <si>
-    <t>A complication is coded from the clinical documentation, so a quarter's count keeps growing after its own coding close. The coding close-out register publishes each quarter at its close and restates it at every close after that; a quarter whose last two publications agree has settled. Four of the ten closed quarters have not, and each cost centre's own finished quarters give the growth still to come.</t>
+    <t>A complication is coded from the clinical documentation, so a quarter's count keeps growing after its own coding close. The coding close-out register publishes each quarter at its close and restates it at every close after that; a quarter whose last two publications agree has settled. Five of the ten closed quarters have not, and the register holds each of the five at a different close: the most recent at its first publication alone. Each cost centre's own finished quarters give the growth still to come.</t>
   </si>
   <si>
     <t>Cost centre 41510</t>
